--- a/excel-projects/RA_Operations_PMO_Executive_Dashboard.xlsx
+++ b/excel-projects/RA_Operations_PMO_Executive_Dashboard.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="R6cde242ad0ed4ecb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" r:id="R40f1c6136a884924"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="R9e8ccaa42cb04428"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAID" sheetId="4" r:id="R1d9cc0c77cb84710"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="Rd7a61310c8944cb7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" r:id="Rc413318fb7f34edb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Projects" sheetId="2" r:id="R8befc240b49f46cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasks" sheetId="3" r:id="R38155ea231fa4172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RAID" sheetId="4" r:id="R36462c800e254ef7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="5" r:id="R3804a489d9e54a59"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -548,7 +548,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R71a3725f454f4480"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R3e84e9ddf4ff45ea"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -578,7 +578,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb3753730523746e1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc4e2576fe1464f7a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1418,7 +1418,7 @@
     </x:cfRule>
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd74dddc92fd84267"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc2579b62e3eb46a6"/>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
@@ -1502,7 +1502,7 @@
         <x:v>COO</x:v>
       </x:c>
       <x:c r="C2" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="D2" s="10" t="n">
         <x:v>46235</x:v>
@@ -1547,7 +1547,7 @@
         <x:v>CFO</x:v>
       </x:c>
       <x:c r="C3" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="D3" s="10" t="n">
         <x:v>46238</x:v>
@@ -1592,7 +1592,7 @@
         <x:v>CX Director</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="D4" s="10" t="n">
         <x:v>46241</x:v>
@@ -1637,7 +1637,7 @@
         <x:v>Supply Chain Director</x:v>
       </x:c>
       <x:c r="C5" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="D5" s="10" t="n">
         <x:v>46244</x:v>
@@ -1682,7 +1682,7 @@
         <x:v>Operations Director</x:v>
       </x:c>
       <x:c r="C6" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="D6" s="10" t="n">
         <x:v>46247</x:v>
@@ -1727,7 +1727,7 @@
         <x:v>HR Director</x:v>
       </x:c>
       <x:c r="C7" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="D7" s="10" t="n">
         <x:v>46250</x:v>
@@ -1792,7 +1792,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rce3187122f3448ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdcd74987c8964f0b"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -1880,7 +1880,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D2" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E2" s="15" t="str">
         <x:v>Completed</x:v>
@@ -1919,7 +1919,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D3" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -1956,7 +1956,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D4" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -1993,7 +1993,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D5" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E5" s="15" t="str">
         <x:v>Blocked</x:v>
@@ -2030,7 +2030,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D6" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -2067,7 +2067,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D7" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2106,7 +2106,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D8" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2143,7 +2143,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D9" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2182,7 +2182,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D10" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E10" s="15" t="str">
         <x:v>Blocked</x:v>
@@ -2219,7 +2219,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D11" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E11" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2256,7 +2256,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D12" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E12" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -2293,7 +2293,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D13" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E13" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2332,7 +2332,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D14" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E14" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2369,7 +2369,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D15" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E15" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2406,7 +2406,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D16" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E16" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2445,7 +2445,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D17" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E17" s="15" t="str">
         <x:v>Blocked</x:v>
@@ -2482,7 +2482,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D18" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E18" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -2519,7 +2519,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D19" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E19" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2558,7 +2558,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D20" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E20" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2597,7 +2597,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D21" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E21" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2634,7 +2634,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D22" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E22" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2671,7 +2671,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D23" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E23" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -2708,7 +2708,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D24" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E24" s="15" t="str">
         <x:v>Blocked</x:v>
@@ -2745,7 +2745,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D25" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E25" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2784,7 +2784,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D26" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E26" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2821,7 +2821,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D27" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E27" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2860,7 +2860,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D28" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E28" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -2897,7 +2897,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D29" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E29" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -2934,7 +2934,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D30" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E30" s="15" t="str">
         <x:v>Completed</x:v>
@@ -2973,7 +2973,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D31" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E31" s="15" t="str">
         <x:v>Blocked</x:v>
@@ -3010,7 +3010,7 @@
         <x:v>Governance</x:v>
       </x:c>
       <x:c r="D32" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="E32" s="15" t="str">
         <x:v>Completed</x:v>
@@ -3049,7 +3049,7 @@
         <x:v>Reporting</x:v>
       </x:c>
       <x:c r="D33" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="E33" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -3086,7 +3086,7 @@
         <x:v>Service</x:v>
       </x:c>
       <x:c r="D34" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="E34" s="15" t="str">
         <x:v>Not Started</x:v>
@@ -3123,7 +3123,7 @@
         <x:v>Inventory</x:v>
       </x:c>
       <x:c r="D35" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="E35" s="15" t="str">
         <x:v>Completed</x:v>
@@ -3162,7 +3162,7 @@
         <x:v>Process</x:v>
       </x:c>
       <x:c r="D36" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="E36" s="15" t="str">
         <x:v>In Progress</x:v>
@@ -3199,7 +3199,7 @@
         <x:v>Analytics</x:v>
       </x:c>
       <x:c r="D37" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="E37" s="15" t="str">
         <x:v>Completed</x:v>
@@ -3265,7 +3265,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd6cc3cf5c74440a8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7fbe3d36be3e4fc3"/>
   </x:tableParts>
   <x:extLst>
     <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
@@ -3348,7 +3348,7 @@
         <x:v>Decision approvals may delay stage gates</x:v>
       </x:c>
       <x:c r="E2" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="F2" s="15" t="str">
         <x:v>High</x:v>
@@ -3380,7 +3380,7 @@
         <x:v>Source systems refresh timing</x:v>
       </x:c>
       <x:c r="E3" s="15" t="str">
-        <x:v>A. Hassan</x:v>
+        <x:v>Owner B</x:v>
       </x:c>
       <x:c r="F3" s="15" t="str">
         <x:v>Medium</x:v>
@@ -3412,7 +3412,7 @@
         <x:v>SLA backlog above target</x:v>
       </x:c>
       <x:c r="E4" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="F4" s="15" t="str">
         <x:v>High</x:v>
@@ -3444,7 +3444,7 @@
         <x:v>Cycle count variance remains volatile</x:v>
       </x:c>
       <x:c r="E5" s="15" t="str">
-        <x:v>S. Omar</x:v>
+        <x:v>Owner D</x:v>
       </x:c>
       <x:c r="F5" s="15" t="str">
         <x:v>High</x:v>
@@ -3476,7 +3476,7 @@
         <x:v>Shift staffing remains stable</x:v>
       </x:c>
       <x:c r="E6" s="15" t="str">
-        <x:v>N. Ali</x:v>
+        <x:v>Owner E</x:v>
       </x:c>
       <x:c r="F6" s="15" t="str">
         <x:v>Medium</x:v>
@@ -3508,7 +3508,7 @@
         <x:v>Candidate source labels inconsistent</x:v>
       </x:c>
       <x:c r="E7" s="15" t="str">
-        <x:v>F. Saleh</x:v>
+        <x:v>Owner F</x:v>
       </x:c>
       <x:c r="F7" s="15" t="str">
         <x:v>Medium</x:v>
@@ -3540,7 +3540,7 @@
         <x:v>Steering committee calendar</x:v>
       </x:c>
       <x:c r="E8" s="15" t="str">
-        <x:v>R. Albloushi</x:v>
+        <x:v>Owner A</x:v>
       </x:c>
       <x:c r="F8" s="15" t="str">
         <x:v>Medium</x:v>
@@ -3572,7 +3572,7 @@
         <x:v>Repeat contacts increasing</x:v>
       </x:c>
       <x:c r="E9" s="15" t="str">
-        <x:v>M. Khan</x:v>
+        <x:v>Owner C</x:v>
       </x:c>
       <x:c r="F9" s="15" t="str">
         <x:v>Medium</x:v>
@@ -3609,7 +3609,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82c36de55e6a456a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4bf83e33d5464f71"/>
   </x:tableParts>
 </x:worksheet>
 </file>
